--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2020_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2020_maule.xlsx
@@ -63,12 +63,12 @@
     <t xml:space="preserve">Colbún</t>
   </si>
   <si>
+    <t xml:space="preserve">San Javier</t>
+  </si>
+  <si>
     <t xml:space="preserve">Curepto</t>
   </si>
   <si>
-    <t xml:space="preserve">San Javier</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pelarco</t>
   </si>
   <si>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:20</t>
+    <t xml:space="preserve">2026-09-09 23:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -732,7 +732,7 @@
         <v>15</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>7103</v>
+        <v>7406</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2020</v>
@@ -749,7 +749,7 @@
         <v>16</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>7406</v>
+        <v>7103</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2020</v>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2020_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2020_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:16</t>
+    <t xml:space="preserve">2026-09-17 14:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2020_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2020_maule.xlsx
@@ -63,12 +63,12 @@
     <t xml:space="preserve">Colbún</t>
   </si>
   <si>
+    <t xml:space="preserve">Curepto</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Javier</t>
   </si>
   <si>
-    <t xml:space="preserve">Curepto</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pelarco</t>
   </si>
   <si>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:11</t>
+    <t xml:space="preserve">2026-09-23 12:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -732,7 +732,7 @@
         <v>15</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>7406</v>
+        <v>7103</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2020</v>
@@ -749,7 +749,7 @@
         <v>16</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>7103</v>
+        <v>7406</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2020</v>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2020_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2020_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:40</t>
+    <t xml:space="preserve">2026-10-02 14:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2020_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2020_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:07</t>
+    <t xml:space="preserve">2026-10-05 11:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
